--- a/Assessment Questions/CDE/Big Data Foundation/BIG DATA INTRODUCTION/What is Big Data and Hadoop/What is Big Data and Hadoop.xlsx
+++ b/Assessment Questions/CDE/Big Data Foundation/BIG DATA INTRODUCTION/What is Big Data and Hadoop/What is Big Data and Hadoop.xlsx
@@ -1,195 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
-  <si>
-    <t>Record_ID,Timestamp,User_ID,Event_Type,Data_Size_MB,Processing_Time_Sec,Node_ID,Node_Type,Rack_ID,Data_Block_ID,Replication_Factor,Block_Size_MB,HDFS_Path,Map_Tasks,Reduce_Tasks,Shuffle_Data_MB,Job_Completion_Time_Sec,Cluster_Name,Data_Node_Count,NameNode_Status,Resource_Manager,Job_Tracker,Hadoop_Distribution,File_Format,Compression_Codec,Input_Splits,Data_Local_Tasks,Rack_Local_Tasks,Speculative_Tasks,Failed_Tasks</t>
-  </si>
-  <si>
-    <t>BD-H-001,2024-03-01 00:00:01,USR-10001,Click,128,45,DN-01,DataNode,Rack-1,BLK-001,3,128, /user/data/logs/2024/03/01/click.log,4,2,256,120,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,8,6,2,1,0</t>
-  </si>
-  <si>
-    <t>BD-H-002,2024-03-01 00:00:02,USR-10002,Page_View,256,78,DN-02,DataNode,Rack-1,BLK-002,3,128, /user/data/logs/2024/03/01/pageview.log,8,4,512,210,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,16,12,3,2,0</t>
-  </si>
-  <si>
-    <t>BD-H-003,2024-03-01 00:00:03,USR-10003,Search,64,23,DN-03,DataNode,Rack-2,BLK-003,3,128, /user/data/logs/2024/03/01/search.log,2,1,128,67,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,4,3,1,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-004,2024-03-01 00:00:04,USR-10004,Purchase,512,156,DN-04,DataNode,Rack-2,BLK-004,3,128, /user/data/transactions/2024/03/01/purchase.parquet,16,8,1024,380,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,32,24,6,3,0</t>
-  </si>
-  <si>
-    <t>BD-H-005,2024-03-01 00:00:05,USR-10005,Add_to_Cart,32,12,DN-05,DataNode,Rack-3,BLK-005,3,128, /user/data/logs/2024/03/01/cart.log,1,1,64,34,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,None,2,2,0,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-006,2024-03-01 00:00:06,USR-10006,Login,16,8,DN-06,DataNode,Rack-3,BLK-006,3,128, /user/data/logs/2024/03/01/login.log,1,1,32,22,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,1,1,0,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-007,2024-03-01 00:00:07,USR-10007,Review,96,34,DN-07,DataNode,Rack-1,BLK-007,3,128, /user/data/reviews/2024/03/01/review.json,3,2,192,98,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,Snappy,6,5,1,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-008,2024-03-01 00:00:08,USR-10008,Logout,8,4,DN-08,DataNode,Rack-1,BLK-008,3,128, /user/data/logs/2024/03/01/logout.log,1,1,16,11,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,1,1,0,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-009,2024-03-01 00:00:09,USR-10009,Click,128,43,DN-09,DataNode,Rack-2,BLK-009,3,128, /user/data/logs/2024/03/01/click.log,4,2,256,115,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,8,6,2,1,0</t>
-  </si>
-  <si>
-    <t>BD-H-010,2024-03-01 00:00:10,USR-10010,Search,64,21,DN-10,DataNode,Rack-2,BLK-010,3,128, /user/data/logs/2024/03/01/search.log,2,1,128,62,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,4,3,1,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-011,2024-03-01 00:00:11,USR-10011,Purchase,1024,312,DN-11,DataNode,Rack-3,BLK-011,3,128, /user/data/transactions/2024/03/01/purchase.parquet,32,16,2048,780,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,64,48,12,5,1</t>
-  </si>
-  <si>
-    <t>BD-H-012,2024-03-01 00:00:12,USR-10012,Page_View,256,76,DN-12,DataNode,Rack-3,BLK-012,3,128, /user/data/logs/2024/03/01/pageview.log,8,4,512,205,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,16,12,3,2,0</t>
-  </si>
-  <si>
-    <t>BD-H-013,2024-03-01 00:00:13,USR-10013,Click,128,44,DN-01,DataNode,Rack-1,BLK-013,3,128, /user/data/logs/2024/03/01/click.log,4,2,256,118,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,8,6,2,1,0</t>
-  </si>
-  <si>
-    <t>BD-H-014,2024-03-01 00:00:14,USR-10014,Add_to_Cart,48,18,DN-02,DataNode,Rack-1,BLK-014,3,128, /user/data/logs/2024/03/01/cart.log,2,1,96,52,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,None,3,2,1,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-015,2024-03-01 00:00:15,USR-10015,Search,96,32,DN-03,DataNode,Rack-2,BLK-015,3,128, /user/data/logs/2024/03/01/search.log,3,2,192,95,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,6,5,1,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-016,2024-03-01 00:00:16,USR-10016,Purchase,768,234,DN-04,DataNode,Rack-2,BLK-016,3,128, /user/data/transactions/2024/03/01/purchase.parquet,24,12,1536,590,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,48,36,9,4,0</t>
-  </si>
-  <si>
-    <t>BD-H-017,2024-03-01 00:00:17,USR-10017,Review,128,45,DN-05,DataNode,Rack-3,BLK-017,3,128, /user/data/reviews/2024/03/01/review.json,4,2,256,123,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,Snappy,8,6,2,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-018,2024-03-01 00:00:18,USR-10018,Login,16,7,DN-06,DataNode,Rack-3,BLK-018,3,128, /user/data/logs/2024/03/01/login.log,1,1,32,20,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,1,1,0,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-019,2024-03-01 00:00:19,USR-10019,Click,192,67,DN-07,DataNode,Rack-1,BLK-019,3,128, /user/data/logs/2024/03/01/click.log,6,3,384,178,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,12,9,2,1,0</t>
-  </si>
-  <si>
-    <t>BD-H-020,2024-03-01 00:00:20,USR-10020,Page_View,384,112,DN-08,DataNode,Rack-1,BLK-020,3,128, /user/data/logs/2024/03/01/pageview.log,12,6,768,298,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,24,18,4,2,0</t>
-  </si>
-  <si>
-    <t>BD-H-021,2024-03-01 00:00:21,USR-10021,Search,80,27,DN-09,DataNode,Rack-2,BLK-021,3,128, /user/data/logs/2024/03/01/search.log,3,2,160,78,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,5,4,1,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-022,2024-03-01 00:00:22,USR-10022,Purchase,896,278,DN-10,DataNode,Rack-2,BLK-022,3,128, /user/data/transactions/2024/03/01/purchase.parquet,28,14,1792,695,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,56,42,10,4,0</t>
-  </si>
-  <si>
-    <t>BD-H-023,2024-03-01 00:00:23,USR-10023,Add_to_Cart,64,24,DN-11,DataNode,Rack-3,BLK-023,3,128, /user/data/logs/2024/03/01/cart.log,2,1,128,68,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,None,4,3,1,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-024,2024-03-01 00:00:24,USR-10024,Review,160,56,DN-12,DataNode,Rack-3,BLK-024,3,128, /user/data/reviews/2024/03/01/review.json,5,3,320,156,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,Snappy,10,8,2,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-025,2024-03-01 00:00:25,USR-10025,Click,256,89,DN-01,DataNode,Rack-1,BLK-025,3,128, /user/data/logs/2024/03/01/click.log,8,4,512,245,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,16,12,3,2,0</t>
-  </si>
-  <si>
-    <t>BD-H-026,2024-03-01 00:00:26,USR-10026,Page_View,320,94,DN-02,DataNode,Rack-1,BLK-026,3,128, /user/data/logs/2024/03/01/pageview.log,10,5,640,256,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,20,15,4,1,0</t>
-  </si>
-  <si>
-    <t>BD-H-027,2024-03-01 00:00:27,USR-10027,Search,112,38,DN-03,DataNode,Rack-2,BLK-027,3,128, /user/data/logs/2024/03/01/search.log,4,2,224,108,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,7,5,2,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-028,2024-03-01 00:00:28,USR-10028,Purchase,640,195,DN-04,DataNode,Rack-2,BLK-028,3,128, /user/data/transactions/2024/03/01/purchase.parquet,20,10,1280,489,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,40,30,8,3,0</t>
-  </si>
-  <si>
-    <t>BD-H-029,2024-03-01 00:00:29,USR-10029,Login,24,10,DN-05,DataNode,Rack-3,BLK-029,3,128, /user/data/logs/2024/03/01/login.log,1,1,48,28,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,2,2,0,0,0</t>
-  </si>
-  <si>
-    <t>BD-H-030,2024-03-01 00:00:30,USR-10030,Logout,12,6,DN-06,DataNode,Rack-3,BLK-030,3,128, /user/data/logs/2024/03/01/logout.log,1,1,24,17,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,1,1,0,0,0</t>
-  </si>
-  <si>
-    <t>Q.No,Question,Big_Data_Hadoop_Concept,Analysis_Required,Expected_Answer,Key_Learning</t>
-  </si>
-  <si>
-    <t>1,"What is Big Data? Define Big Data and explain why traditional databases cannot handle it using metrics from the dataset.","Big Data Definition","Analyze data volume, velocity, variety","Data Volume: 8,192 MB in 30 seconds = 1 TB/day; Velocity: 1 record/sec; Variety: 5 formats. Traditional RDBMS cannot handle this scale, speed, and variety","Big Data requires distributed systems like Hadoop to handle volume, velocity, and variety"</t>
-  </si>
-  <si>
-    <t>2,"What is Hadoop? Explain the core components of Hadoop architecture. Identify them in the dataset.","Hadoop Architecture","Identify HDFS, YARN, MapReduce components","HDFS: DataNode, NameNode, Block; YARN: Resource Manager; MapReduce: Map/Reduce tasks. Dataset shows DataNode-01 to 12, NameNode Active, Resource Manager YARN","Hadoop has three core components: HDFS (storage), YARN (resource management), MapReduce (processing)"</t>
-  </si>
-  <si>
-    <t>3,"What is HDFS (Hadoop Distributed File System)? How does it store data? Analyze block size and replication.","HDFS Storage","Analyze Block_Size_MB, Replication_Factor, Data_Block_ID","Block Size: 128 MB; Replication Factor: 3; Data stored across 12 DataNodes in 3 racks. Each block replicated 3 times for fault tolerance","HDFS splits files into blocks (128MB default) and replicates them across nodes for fault tolerance"</t>
-  </si>
-  <si>
-    <t>4,"What is data replication in HDFS? Why is replication factor 3 used? Calculate total storage with replication.","HDFS Replication","Calculate total raw data vs actual storage","Raw Data: 8,192 MB; With replication factor 3: 24,576 MB actual storage. Replication ensures data durability and availability","Replication factor 3 provides fault tolerance - if one node fails, data available on 2 others"</t>
-  </si>
-  <si>
-    <t>5,"What is a DataNode and NameNode in HDFS? Identify their roles from the dataset.","HDFS Architecture","Analyze Node_ID, Node_Type, NameNode_Status","DataNodes (DN-01 to DN-12): Store data blocks; NameNode: Active status, manages metadata; Racks: Rack-1,2,3 organize nodes","NameNode is the master (metadata), DataNodes are slaves (data storage)"</t>
-  </si>
-  <si>
-    <t>6,"What is YARN (Yet Another Resource Negotiator)? How does it manage resources? Identify YARN components.","YARN Resource Management","Analyze Resource_Manager, Node_Type, Job_Tracker","Resource Manager: YARN manages cluster resources; Job History tracks completed jobs; Nodes execute tasks","YARN separates resource management from job scheduling for better cluster utilization"</t>
-  </si>
-  <si>
-    <t>7,"What is MapReduce? Explain the Map and Reduce phases using the dataset metrics.","MapReduce Processing","Analyze Map_Tasks, Reduce_Tasks, Shuffle_Data_MB","Map tasks: 1-32 per job (parallel processing); Reduce tasks: 1-16 (aggregation); Shuffle data: 16-2048 MB transferred between phases","Map: parallel processing; Shuffle: data transfer; Reduce: aggregation and final output"</t>
-  </si>
-  <si>
-    <t>8,"Calculate the total data processed, total map tasks, and total reduce tasks. What is the ratio?","MapReduce Metrics","Sum Data_Size_MB, Map_Tasks, Reduce_Tasks","Total Data: 8,192 MB; Total Map Tasks: 208; Total Reduce Tasks: 104; Map:Reduce ratio = 2:1","Map tasks typically outnumber reduce tasks; ratio depends on data and processing needs"</t>
-  </si>
-  <si>
-    <t>9,"What is data locality in Hadoop? Calculate data-local vs rack-local tasks from the dataset.","Data Locality","Analyze Data_Local_Tasks, Rack_Local_Tasks","Data Local Tasks: 85%; Rack Local Tasks: 12%; Cross-Rack: 3%. Data locality improves performance","Moving computation to data (not data to computation) reduces network traffic and improves performance"</t>
-  </si>
-  <si>
-    <t>10,"What is speculative execution in Hadoop? How many speculative tasks were run?","Speculative Execution","Analyze Speculative_Tasks column","Speculative Tasks: 29 across all jobs. Hadoop runs backup tasks for slow-running tasks to prevent job delay","Speculative execution handles stragglers (slow nodes) by running duplicate tasks"</t>
-  </si>
-  <si>
-    <t>11,"What are the different Hadoop distributions? Which distribution is used in the dataset?","Hadoop Distributions","Analyze Hadoop_Distribution column","Cloudera distribution used. Other distributions: Apache Hadoop, Hortonworks (now Cloudera), MapR","Different vendors provide enterprise Hadoop distributions with additional tools and support"</t>
-  </si>
-  <si>
-    <t>12,"What file formats are supported in Hadoop? Identify formats used and their compression codecs.","Hadoop File Formats","Analyze File_Format, Compression_Codec","Formats: Parquet (40%), Avro (30%), JSON (20%), Others (10%); Compression: Snappy (60%), Gzip (20%), None (20%)","Columnar formats (Parquet) are efficient for analytics; Avro for schema evolution; JSON for flexibility"</t>
-  </si>
-  <si>
-    <t>13,"What is data skew in MapReduce? Identify which job had the highest shuffle data and what that indicates.","Data Skew","Find max Shuffle_Data_MB; Analyze corresponding Map/Reduce tasks","Job with 2,048 MB shuffle data (32 map tasks, 16 reduce tasks). Indicates potential data skew or large aggregation","Data skew can cause some reducers to process much more data than others, slowing the job"</t>
-  </si>
-  <si>
-    <t>14,"Calculate the average job completion time. What is the relationship between data size and completion time?","Job Performance","Correlate Data_Size_MB with Job_Completion_Time_Sec","Average completion: 156 seconds; Correlation: Larger data takes longer; 1,024 MB takes 312 sec vs 16 MB takes 8 sec","Processing time scales with data size; Hadoop handles large data through parallel processing"</t>
-  </si>
-  <si>
-    <t>15,"What is the Hadoop ecosystem? List ecosystem tools that could be used with this data.","Hadoop Ecosystem","Based on data types and use cases","Hive: SQL queries; HBase: real-time access; Spark: faster processing; Pig: scripting; Sqoop: data import; Flume: log collection","Hadoop ecosystem includes many tools for different data processing needs"</t>
-  </si>
-  <si>
-    <t>16,"How does Hadoop achieve fault tolerance? Calculate the impact if one DataNode fails.","Fault Tolerance","Analyze Replication_Factor, Node count","With replication factor 3, if one DataNode fails, data still available on 2 other nodes. 12 nodes with 3 replicas = 4x data redundancy","HDFS replication ensures no data loss; NameNode secondary for metadata backup"</t>
-  </si>
-  <si>
-    <t>17,"What is the difference between Hadoop 1.x and Hadoop 2.x? Identify components from dataset.","Hadoop Versions","Analyze Resource_Manager presence","Hadoop 2.x features: YARN (present), Resource Manager, separates resource management from MapReduce","Hadoop 2.x introduced YARN for better resource management beyond MapReduce"</t>
-  </si>
-  <si>
-    <t>18,"What is a Rack in Hadoop? How does rack awareness improve performance?","Rack Awareness","Analyze Rack_ID distribution","3 racks: Rack-1,2,3. Data-local tasks (85%) and rack-local tasks (12%) minimize cross-rack network traffic","Rack awareness places replicas across racks to prevent rack failure from causing data loss"</t>
-  </si>
-  <si>
-    <t>19,"Calculate the total storage capacity needed for 1 month of data at this rate. Include replication.","Capacity Planning","Extrapolate daily data, multiply by 30, include replication","Daily raw data: 23.6 GB; Monthly raw: 708 GB; With replication factor 3: 2.1 TB storage needed","Capacity planning must account for data growth and replication overhead"</t>
-  </si>
-  <si>
-    <t>20,"What is Hadoop's role in modern Big Data architecture? Create a high-level architecture diagram from dataset components.","Hadoop Architecture","Map all components to architecture layers","Data Ingestion → HDFS Storage (NameNode, DataNode) → YARN Resource Management → MapReduce Processing → Output","Hadoop provides distributed storage and processing foundation for Big Data analytics"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -199,33 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,285 +316,983 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Record_ID,Timestamp,User_ID,Event_Type,Data_Size_MB,Processing_Time_Sec,Node_ID,Node_Type,Rack_ID,Data_Block_ID,Replication_Factor,Block_Size_MB,HDFS_Path,Map_Tasks,Reduce_Tasks,Shuffle_Data_MB,Job_Completion_Time_Sec,Cluster_Name,Data_Node_Count,NameNode_Status,Resource_Manager,Job_Tracker,Hadoop_Distribution,File_Format,Compression_Codec,Input_Splits,Data_Local_Tasks,Rack_Local_Tasks,Speculative_Tasks,Failed_Tasks</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-001,2024-03-01 00:00:01,USR-10001,Click,128,45,DN-01,DataNode,Rack-1,BLK-001,3,128, /user/data/logs/2024/03/01/click.log,4,2,256,120,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,8,6,2,1,0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-002,2024-03-01 00:00:02,USR-10002,Page_View,256,78,DN-02,DataNode,Rack-1,BLK-002,3,128, /user/data/logs/2024/03/01/pageview.log,8,4,512,210,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,16,12,3,2,0</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-003,2024-03-01 00:00:03,USR-10003,Search,64,23,DN-03,DataNode,Rack-2,BLK-003,3,128, /user/data/logs/2024/03/01/search.log,2,1,128,67,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,4,3,1,0,0</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-004,2024-03-01 00:00:04,USR-10004,Purchase,512,156,DN-04,DataNode,Rack-2,BLK-004,3,128, /user/data/transactions/2024/03/01/purchase.parquet,16,8,1024,380,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,32,24,6,3,0</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-005,2024-03-01 00:00:05,USR-10005,Add_to_Cart,32,12,DN-05,DataNode,Rack-3,BLK-005,3,128, /user/data/logs/2024/03/01/cart.log,1,1,64,34,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,None,2,2,0,0,0</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-006,2024-03-01 00:00:06,USR-10006,Login,16,8,DN-06,DataNode,Rack-3,BLK-006,3,128, /user/data/logs/2024/03/01/login.log,1,1,32,22,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,1,1,0,0,0</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-007,2024-03-01 00:00:07,USR-10007,Review,96,34,DN-07,DataNode,Rack-1,BLK-007,3,128, /user/data/reviews/2024/03/01/review.json,3,2,192,98,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,Snappy,6,5,1,0,0</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-008,2024-03-01 00:00:08,USR-10008,Logout,8,4,DN-08,DataNode,Rack-1,BLK-008,3,128, /user/data/logs/2024/03/01/logout.log,1,1,16,11,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,1,1,0,0,0</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-009,2024-03-01 00:00:09,USR-10009,Click,128,43,DN-09,DataNode,Rack-2,BLK-009,3,128, /user/data/logs/2024/03/01/click.log,4,2,256,115,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,8,6,2,1,0</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-010,2024-03-01 00:00:10,USR-10010,Search,64,21,DN-10,DataNode,Rack-2,BLK-010,3,128, /user/data/logs/2024/03/01/search.log,2,1,128,62,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,4,3,1,0,0</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-011,2024-03-01 00:00:11,USR-10011,Purchase,1024,312,DN-11,DataNode,Rack-3,BLK-011,3,128, /user/data/transactions/2024/03/01/purchase.parquet,32,16,2048,780,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,64,48,12,5,1</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-012,2024-03-01 00:00:12,USR-10012,Page_View,256,76,DN-12,DataNode,Rack-3,BLK-012,3,128, /user/data/logs/2024/03/01/pageview.log,8,4,512,205,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,16,12,3,2,0</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-013,2024-03-01 00:00:13,USR-10013,Click,128,44,DN-01,DataNode,Rack-1,BLK-013,3,128, /user/data/logs/2024/03/01/click.log,4,2,256,118,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,8,6,2,1,0</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-014,2024-03-01 00:00:14,USR-10014,Add_to_Cart,48,18,DN-02,DataNode,Rack-1,BLK-014,3,128, /user/data/logs/2024/03/01/cart.log,2,1,96,52,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,None,3,2,1,0,0</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-015,2024-03-01 00:00:15,USR-10015,Search,96,32,DN-03,DataNode,Rack-2,BLK-015,3,128, /user/data/logs/2024/03/01/search.log,3,2,192,95,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,6,5,1,0,0</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-016,2024-03-01 00:00:16,USR-10016,Purchase,768,234,DN-04,DataNode,Rack-2,BLK-016,3,128, /user/data/transactions/2024/03/01/purchase.parquet,24,12,1536,590,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,48,36,9,4,0</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-017,2024-03-01 00:00:17,USR-10017,Review,128,45,DN-05,DataNode,Rack-3,BLK-017,3,128, /user/data/reviews/2024/03/01/review.json,4,2,256,123,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,Snappy,8,6,2,0,0</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-018,2024-03-01 00:00:18,USR-10018,Login,16,7,DN-06,DataNode,Rack-3,BLK-018,3,128, /user/data/logs/2024/03/01/login.log,1,1,32,20,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,1,1,0,0,0</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-019,2024-03-01 00:00:19,USR-10019,Click,192,67,DN-07,DataNode,Rack-1,BLK-019,3,128, /user/data/logs/2024/03/01/click.log,6,3,384,178,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,12,9,2,1,0</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-020,2024-03-01 00:00:20,USR-10020,Page_View,384,112,DN-08,DataNode,Rack-1,BLK-020,3,128, /user/data/logs/2024/03/01/pageview.log,12,6,768,298,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,24,18,4,2,0</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-021,2024-03-01 00:00:21,USR-10021,Search,80,27,DN-09,DataNode,Rack-2,BLK-021,3,128, /user/data/logs/2024/03/01/search.log,3,2,160,78,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,5,4,1,0,0</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-022,2024-03-01 00:00:22,USR-10022,Purchase,896,278,DN-10,DataNode,Rack-2,BLK-022,3,128, /user/data/transactions/2024/03/01/purchase.parquet,28,14,1792,695,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,56,42,10,4,0</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-023,2024-03-01 00:00:23,USR-10023,Add_to_Cart,64,24,DN-11,DataNode,Rack-3,BLK-023,3,128, /user/data/logs/2024/03/01/cart.log,2,1,128,68,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,None,4,3,1,0,0</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-024,2024-03-01 00:00:24,USR-10024,Review,160,56,DN-12,DataNode,Rack-3,BLK-024,3,128, /user/data/reviews/2024/03/01/review.json,5,3,320,156,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,JSON,Snappy,10,8,2,0,0</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-025,2024-03-01 00:00:25,USR-10025,Click,256,89,DN-01,DataNode,Rack-1,BLK-025,3,128, /user/data/logs/2024/03/01/click.log,8,4,512,245,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,16,12,3,2,0</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-026,2024-03-01 00:00:26,USR-10026,Page_View,320,94,DN-02,DataNode,Rack-1,BLK-026,3,128, /user/data/logs/2024/03/01/pageview.log,10,5,640,256,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Snappy,20,15,4,1,0</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-027,2024-03-01 00:00:27,USR-10027,Search,112,38,DN-03,DataNode,Rack-2,BLK-027,3,128, /user/data/logs/2024/03/01/search.log,4,2,224,108,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,Snappy,7,5,2,0,0</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>28</v>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-028,2024-03-01 00:00:28,USR-10028,Purchase,640,195,DN-04,DataNode,Rack-2,BLK-028,3,128, /user/data/transactions/2024/03/01/purchase.parquet,20,10,1280,489,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Parquet,Gzip,40,30,8,3,0</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-029,2024-03-01 00:00:29,USR-10029,Login,24,10,DN-05,DataNode,Rack-3,BLK-029,3,128, /user/data/logs/2024/03/01/login.log,1,1,48,28,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,2,2,0,0,0</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>30</v>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>BD-H-030,2024-03-01 00:00:30,USR-10030,Logout,12,6,DN-06,DataNode,Rack-3,BLK-030,3,128, /user/data/logs/2024/03/01/logout.log,1,1,24,17,Prod-Cluster,128,Active,YARN,JobHistory,Cloudera,Avro,None,1,1,0,0,0</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>31</v>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data? Define Big Data and explain why traditional databases cannot handle it using metrics from the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Analyze data volume, velocity, variety | Data Volume: 8,192 MB in 30 seconds = 1 TB/day; Velocity: 1 record/sec; Variety: 5 formats. Traditional RDBMS cannot handle this scale, speed, and variety</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Big Data requires distributed systems like Hadoop to handle volume, velocity, and variety</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>What is Hadoop? Explain the core components of Hadoop architecture. Identify them in the dataset.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Identify HDFS, YARN, MapReduce components | HDFS: DataNode, NameNode, Block; YARN: Resource Manager; MapReduce: Map/Reduce tasks. Dataset shows DataNode-01 to 12, NameNode Active, Resource Manager YARN</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop has three core components: HDFS (storage), YARN (resource management), MapReduce (processing)</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What is HDFS (Hadoop Distributed File System)? How does it store data? Analyze block size and replication.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Block_Size_MB, Replication_Factor, Data_Block_ID | Block Size: 128 MB; Replication Factor: 3; Data stored across 12 DataNodes in 3 racks. Each block replicated 3 times for fault tolerance</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>HDFS splits files into blocks (128MB default) and replicates them across nodes for fault tolerance</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>What is data replication in HDFS? Why is replication factor 3 used? Calculate total storage with replication.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Calculate total raw data vs actual storage | Raw Data: 8,192 MB; With replication factor 3: 24,576 MB actual storage. Replication ensures data durability and availability</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Replication factor 3 provides fault tolerance - if one node fails, data available on 2 others</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>What is a DataNode and NameNode in HDFS? Identify their roles from the dataset.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Node_ID, Node_Type, NameNode_Status | DataNodes (DN-01 to DN-12): Store data blocks; NameNode: Active status, manages metadata; Racks: Rack-1,2,3 organize nodes</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>NameNode is the master (metadata), DataNodes are slaves (data storage)</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>What is YARN (Yet Another Resource Negotiator)? How does it manage resources? Identify YARN components.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Resource_Manager, Node_Type, Job_Tracker | Resource Manager: YARN manages cluster resources; Job History tracks completed jobs; Nodes execute tasks</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>YARN separates resource management from job scheduling for better cluster utilization</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What is MapReduce? Explain the Map and Reduce phases using the dataset metrics.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Map_Tasks, Reduce_Tasks, Shuffle_Data_MB | Map tasks: 1-32 per job (parallel processing); Reduce tasks: 1-16 (aggregation); Shuffle data: 16-2048 MB transferred between phases</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>Map: parallel processing; Shuffle: data transfer; Reduce: aggregation and final output</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Calculate the total data processed, total map tasks, and total reduce tasks. What is the ratio?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Sum Data_Size_MB, Map_Tasks, Reduce_Tasks | Total Data: 8,192 MB; Total Map Tasks: 208; Total Reduce Tasks: 104; Map:Reduce ratio = 2:1</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Map tasks typically outnumber reduce tasks; ratio depends on data and processing needs</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What is data locality in Hadoop? Calculate data-local vs rack-local tasks from the dataset.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Data_Local_Tasks, Rack_Local_Tasks | Data Local Tasks: 85%; Rack Local Tasks: 12%; Cross-Rack: 3%. Data locality improves performance</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Moving computation to data (not data to computation) reduces network traffic and improves performance</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What is speculative execution in Hadoop? How many speculative tasks were run?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Speculative_Tasks column | Speculative Tasks: 29 across all jobs. Hadoop runs backup tasks for slow-running tasks to prevent job delay</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Speculative execution handles stragglers (slow nodes) by running duplicate tasks</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>What are the different Hadoop distributions? Which distribution is used in the dataset?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Hadoop_Distribution column | Cloudera distribution used. Other distributions: Apache Hadoop, Hortonworks (now Cloudera), MapR</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Different vendors provide enterprise Hadoop distributions with additional tools and support</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What file formats are supported in Hadoop? Identify formats used and their compression codecs.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Analyze File_Format, Compression_Codec | Formats: Parquet (40%), Avro (30%), JSON (20%), Others (10%); Compression: Snappy (60%), Gzip (20%), None (20%)</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Columnar formats (Parquet) are efficient for analytics; Avro for schema evolution; JSON for flexibility</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What is data skew in MapReduce? Identify which job had the highest shuffle data and what that indicates.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Find max Shuffle_Data_MB; Analyze corresponding Map/Reduce tasks | Job with 2,048 MB shuffle data (32 map tasks, 16 reduce tasks). Indicates potential data skew or large aggregation</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Data skew can cause some reducers to process much more data than others, slowing the job</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Calculate the average job completion time. What is the relationship between data size and completion time?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Correlate Data_Size_MB with Job_Completion_Time_Sec | Average completion: 156 seconds; Correlation: Larger data takes longer; 1,024 MB takes 312 sec vs 16 MB takes 8 sec</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Processing time scales with data size; Hadoop handles large data through parallel processing</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What is the Hadoop ecosystem? List ecosystem tools that could be used with this data.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Based on data types and use cases | Hive: SQL queries; HBase: real-time access; Spark: faster processing; Pig: scripting; Sqoop: data import; Flume: log collection</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop ecosystem includes many tools for different data processing needs</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>How does Hadoop achieve fault tolerance? Calculate the impact if one DataNode fails.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Replication_Factor, Node count | With replication factor 3, if one DataNode fails, data still available on 2 other nodes. 12 nodes with 3 replicas = 4x data redundancy</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>HDFS replication ensures no data loss; NameNode secondary for metadata backup</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between Hadoop 1.x and Hadoop 2.x? Identify components from dataset.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Resource_Manager presence | Hadoop 2.x features: YARN (present), Resource Manager, separates resource management from MapReduce</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop 2.x introduced YARN for better resource management beyond MapReduce</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What is a Rack in Hadoop? How does rack awareness improve performance?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Rack_ID distribution | 3 racks: Rack-1,2,3. Data-local tasks (85%) and rack-local tasks (12%) minimize cross-rack network traffic</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Rack awareness places replicas across racks to prevent rack failure from causing data loss</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Calculate the total storage capacity needed for 1 month of data at this rate. Include replication.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Extrapolate daily data, multiply by 30, include replication | Daily raw data: 23.6 GB; Monthly raw: 708 GB; With replication factor 3: 2.1 TB storage needed</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Capacity planning must account for data growth and replication overhead</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data and Hadoop</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>What is Hadoop's role in modern Big Data architecture? Create a high-level architecture diagram from dataset components.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Map all components to architecture layers | Data Ingestion → HDFS Storage (NameNode, DataNode) → YARN Resource Management → MapReduce Processing → Output</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop provides distributed storage and processing foundation for Big Data analytics</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>